--- a/public/portfolio/nrv/NRV - Rebranding.xlsx
+++ b/public/portfolio/nrv/NRV - Rebranding.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="105">
   <si>
     <t>How to fill</t>
   </si>
@@ -29,45 +29,45 @@
     <t>EN</t>
   </si>
   <si>
+    <t>ES</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>ES</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
     <t>1. Fill columns PL / EN / ES for each field.</t>
   </si>
   <si>
+    <t>2. Section 1-10 map to case-study sections (max 10). Leave unused sections empty.</t>
+  </si>
+  <si>
+    <t>3. Label = sidebar name (e.g. OVERVIEW, WYZWANIA, RESULTS).</t>
+  </si>
+  <si>
+    <t>4. Title = section heading. Description = body copy.</t>
+  </si>
+  <si>
+    <t>5. Hero Title = project hero headline.</t>
+  </si>
+  <si>
     <t>Project</t>
   </si>
   <si>
-    <t>2. Section 1-10 map to case-study sections (max 10). Leave unused sections empty.</t>
-  </si>
-  <si>
-    <t>3. Label = sidebar name (e.g. OVERVIEW, WYZWANIA, RESULTS).</t>
+    <t>6. Meta: Services, Industry, Market, Year, Live (adres strony, ten sam we wszystkich językach).</t>
+  </si>
+  <si>
+    <t>7. One sheet = one project. Duplicate "Project translations" for more projects.</t>
   </si>
   <si>
     <t>Project name</t>
   </si>
   <si>
-    <t>4. Title = section heading. Description = body copy.</t>
-  </si>
-  <si>
-    <t>5. Hero Title = project hero headline.</t>
-  </si>
-  <si>
     <t>Rebranding NRV Control Systems</t>
   </si>
   <si>
-    <t>6. Meta: Services, Industry, Market, Year, Live (adres strony, ten sam we wszystkich językach).</t>
-  </si>
-  <si>
-    <t>7. One sheet = one project. Duplicate "Project translations" for more projects.</t>
-  </si>
-  <si>
     <t>Wewnętrzna nazwa projektu / folder</t>
   </si>
   <si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>Klient / Client / Cliente</t>
+  </si>
+  <si>
+    <t>NRV Systems</t>
   </si>
   <si>
     <t>NRV Control Systems</t>
@@ -760,7 +763,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>7</v>
@@ -788,19 +791,19 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>18</v>
@@ -837,81 +840,81 @@
         <v>26</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="12">
         <v>2026.0</v>
@@ -923,627 +926,627 @@
         <v>2026.0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" ht="60.0" customHeight="1">
       <c r="A12" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" ht="60.0" customHeight="1">
       <c r="A15" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="19" t="s">
         <v>59</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" ht="60.0" customHeight="1">
       <c r="A18" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" ht="60.0" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" ht="60.0" customHeight="1">
       <c r="A24" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" ht="60.0" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" ht="60.0" customHeight="1">
       <c r="A30" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" ht="60.0" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" ht="60.0" customHeight="1">
       <c r="A36" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" ht="60.0" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
@@ -2563,7 +2566,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -2573,32 +2576,32 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
